--- a/www/download/IND.hours_worked.empe_ms.r.pc.rpA2.xlsx
+++ b/www/download/IND.hours_worked.empe_ms.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>42.44</t>
+          <t>0.424355487050642</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>0.421210131060266</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>0.418086412705438</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>0.414977829109405</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>41.19</t>
+          <t>0.411878533712213</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>40.88</t>
+          <t>0.408783177511304</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>0.405686782442459</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.16</t>
+          <t>0.401636315952333</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>0.398865762962166</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>0.412665252236202</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>0.425671010567606</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>0.425671010567606</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>0.425671010567606</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>0.425671010567606</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>42.57</t>
+          <t>0.425671010567606</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>66.28</t>
+          <t>0.662839720880351</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>66.88</t>
+          <t>0.668796327674197</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>67.31</t>
+          <t>0.673110065127009</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.81</t>
+          <t>0.668064470199833</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>62.71</t>
+          <t>0.627079408305293</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>0.62316661068586</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>62.65</t>
+          <t>0.626513068780862</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>62.21</t>
+          <t>0.622071690226866</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>0.622189505933992</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>57.82</t>
+          <t>0.578248926416643</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>0.590993998342501</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>59.16</t>
+          <t>0.591558462763341</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>0.583330285245219</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>59.54</t>
+          <t>0.595412993275397</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>0.584057539098117</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>0.505332216895786</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51.25</t>
+          <t>0.512543164284425</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.79</t>
+          <t>0.517893931658126</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>52.29</t>
+          <t>0.522917794145958</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>52.71</t>
+          <t>0.527121105523797</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>53.78</t>
+          <t>0.537838422668512</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>0.54431071529447</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>0.548614893014351</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>0.553043006109559</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>55.91</t>
+          <t>0.559063799365315</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>56.43</t>
+          <t>0.564314313288735</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>56.91</t>
+          <t>0.569055971618182</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>56.65</t>
+          <t>0.566531760403428</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>0.540852224446333</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>54.34</t>
+          <t>0.543359516129222</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.223112108065907</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>0.23076560909183</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>0.222322563509499</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213259917236434</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>0.230516427377225</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>0.236222063272243</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>0.243682664860547</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.24066817692975</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>0.235794531713251</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246454552404253</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246466736759821</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>0.255423644330556</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.247899377409721</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>0.244786230180686</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>0.261406427925119</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>0.340784670955906</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>0.351855466310366</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>0.362574578195994</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>0.372962573399857</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>0.383038300726325</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>0.392819098775233</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>0.402320969988155</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>0.4115587281512</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>0.421928881883914</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.431953292642506</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>0.441650600042035</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>0.444694650255785</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>0.447591911401025</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>0.450352104408826</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>0.452984207244345</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>0.690684332302548</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>0.690398853786109</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>0.687386446496856</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>0.680037452762035</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>0.685018990794521</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>0.677638712463395</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>0.668973831811685</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>66.41</t>
+          <t>0.664060624245341</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>65.98</t>
+          <t>0.659763732827066</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>65.56</t>
+          <t>0.655572736587632</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>0.643562910100225</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>0.631862208699721</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>62.13</t>
+          <t>0.621306339865223</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>62.48</t>
+          <t>0.624793958567878</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>60.95</t>
+          <t>0.609462512069951</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>0.546629899811376</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>54.88</t>
+          <t>0.548838413468853</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>55.08</t>
+          <t>0.550801364281165</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>55.25</t>
+          <t>0.552514991559512</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>0.553975924311342</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>55.52</t>
+          <t>0.555181191281473</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>55.61</t>
+          <t>0.556128229751239</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>55.68</t>
+          <t>0.556814893069668</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>54.14</t>
+          <t>0.541427567094029</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>0.529339801865398</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>0.509363172699616</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>0.490667017609051</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>0.492256745633495</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>0.484234311078644</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>48.42</t>
+          <t>0.484234311078644</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>0.318791418436093</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>0.324947408234552</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>0.323839518531987</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>0.322239712489496</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.19</t>
+          <t>0.34188358299065</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>0.341518812849087</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.06</t>
+          <t>0.340604183337239</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>0.335174967524045</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>0.34097972883778</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>0.353023886537293</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>0.371250199764164</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>0.378984137358456</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>0.364026733536202</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>0.36505319998813</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>0.361602696328224</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>0.754187821899948</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>0.754187821899948</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>0.754187821899948</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>0.754187821899948</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>75.08</t>
+          <t>0.750844252058238</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>74.86</t>
+          <t>0.748604720245461</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>74.69</t>
+          <t>0.746933979458665</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>0.742525327707243</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>74.43</t>
+          <t>0.744333331661683</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>73.49</t>
+          <t>0.734923428881216</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>0.73503868811171</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>0.728441663122852</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>0.728606263828352</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>0.718325479796574</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>0.700968852367018</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>0.547261397238165</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.69</t>
+          <t>0.546883703646024</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>54.58</t>
+          <t>0.54577213163059</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>53.22</t>
+          <t>0.532162925542613</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>53.24</t>
+          <t>0.532423285583175</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>0.530032853522447</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>52.45</t>
+          <t>0.524471762274684</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>51.95</t>
+          <t>0.51952664534938</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>50.26</t>
+          <t>0.502607174425204</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>49.75</t>
+          <t>0.497517869906896</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>49.58</t>
+          <t>0.495829042218748</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>50.39</t>
+          <t>0.503949097689891</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>0.51417188019682</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>0.509340315695164</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>0.494468677090216</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>50.87</t>
+          <t>0.508675782751281</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>0.504606716269431</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>0.500097814082655</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>0.495415494514964</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>0.494145247981435</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>49.52</t>
+          <t>0.495230087293385</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>0.489226498135873</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>48.38</t>
+          <t>0.483832875522457</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>0.440663807425436</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>0.436008486739805</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>0.418101348065121</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>0.413438054075713</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>0.409629058751028</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>39.21</t>
+          <t>0.392109697756292</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>0.381033434375838</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>0.1821626674776</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>0.186920463930991</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>0.193639114389821</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>0.193409588457697</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>0.194914432738086</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>0.192934743939011</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>0.189917724510404</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>0.189293303901458</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>0.19146921679359</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>0.195679667526162</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>0.203494393077043</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>20.62</t>
+          <t>0.206234921784515</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>0.206931916231444</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>20.67</t>
+          <t>0.206730720542143</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>0.200809650196341</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>0.435723975581996</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>0.443049763377036</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>0.44686742156449</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>0.450995809736388</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>47.02</t>
+          <t>0.470217032886022</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>0.465455886730267</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>46.26</t>
+          <t>0.462643656485473</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>45.57</t>
+          <t>0.455677040208562</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.460037890308703</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>44.28</t>
+          <t>0.442799612485211</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>0.427497535090145</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>0.428050405386733</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>0.431646911661359</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0.425993440753631</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>0.417506188124432</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>0.368008523162893</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>0.367880723857567</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0.369986768865075</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>37.17</t>
+          <t>0.371659022569424</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>37.39</t>
+          <t>0.373854167498838</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>0.378264091921988</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>0.378315454082997</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>37.87</t>
+          <t>0.378713452745793</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>0.380248042929303</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>0.379982016028651</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>0.380915420278385</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>0.383322416751329</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>37.87</t>
+          <t>0.378743790711091</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>0.376342079570657</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>0.363317495831553</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>0.438206810921495</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>0.43353220079949</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>0.43224025655203</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.18</t>
+          <t>0.431843453646785</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>0.426230583878397</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>42.72</t>
+          <t>0.427204358110527</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>42.52</t>
+          <t>0.425222834471882</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>0.426594183888162</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>0.427720982828358</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>0.421267948810471</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>0.410770351689802</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>0.39679368132054</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>0.397322566028125</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>0.395885708792628</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>37.64</t>
+          <t>0.376390142413893</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>0.423198456607996</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>0.429484250721709</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>0.434865854864508</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>0.424302374678086</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>0.414960978830764</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>0.401713787845467</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>0.391698076797508</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>0.389023972510903</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>0.402012900664355</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>41.44</t>
+          <t>0.414364820017456</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>0.41098262601955</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>0.402893210446118</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>0.378642327524046</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>38.04</t>
+          <t>0.380355654501915</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381639115268523</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>38.98</t>
+          <t>0.389806732039504</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>0.392942559839754</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>0.403611401366628</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>0.413953244239236</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>0.440242378161553</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>0.437661274948664</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>43.78</t>
+          <t>0.437818078117429</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>0.442544999518498</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>0.446890749089195</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>0.448678263348279</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>0.454417753572607</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0.412947613463164</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>0.409051402200585</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>0.414293168663199</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>41.14</t>
+          <t>0.411364260838987</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>0.649554458732762</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>0.649554458732762</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>0.649554458732762</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>64.96</t>
+          <t>0.649554458732762</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>64.53</t>
+          <t>0.645258217041934</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>0.646045157127717</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>0.64700447349709</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>64.84</t>
+          <t>0.648391617038096</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>64.16</t>
+          <t>0.641586985175279</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>0.622177393879664</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>0.614555108075759</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>61.45</t>
+          <t>0.614514263060274</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>61.67</t>
+          <t>0.616739188517966</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>59.29</t>
+          <t>0.59291787242948</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>59.55</t>
+          <t>0.59548173660398</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>32.13</t>
+          <t>0.321256642078374</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>0.330212095108764</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33.99</t>
+          <t>0.339949758690545</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>0.347306032179633</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>0.346217318768818</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>0.365188236607144</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>35.76</t>
+          <t>0.357600269258758</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>0.360761935930122</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>39.03</t>
+          <t>0.390308142254669</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>0.376022104016237</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>0.376281974923109</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>0.376919085587827</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>0.367438698339098</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>0.367438698339098</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>36.74</t>
+          <t>0.367438698339098</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>0.436994576863936</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>0.442056344387016</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.71</t>
+          <t>0.447057917908349</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>0.452006333363979</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>45.69</t>
+          <t>0.456908384743679</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>44.55</t>
+          <t>0.445520803087642</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>0.434692480392781</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>42.44</t>
+          <t>0.42437324948376</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>41.45</t>
+          <t>0.414519441472978</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405092807520488</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405092807520488</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405092807520488</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405092807520488</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405092807520488</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>40.51</t>
+          <t>0.405092807520488</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>0.428464436081877</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>0.427003031213508</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>0.430957855872728</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>0.420055005105466</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>0.410277061491551</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>0.402898681511019</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>39.18</t>
+          <t>0.39175902868817</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>0.377963162359787</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>0.363383196416057</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>34.38</t>
+          <t>0.343776242687223</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>0.341260703375215</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>33.21</t>
+          <t>0.332075520686761</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>0.325329795878304</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>0.314234256124497</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>29.91</t>
+          <t>0.299144275317575</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>0.472036348240102</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.12</t>
+          <t>0.481218432167405</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>0.489860173111289</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>0.497641148403368</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>0.498564435935901</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>0.517194075933086</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>0.495523369331111</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>0.495023115143772</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>0.501993812675581</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>0.529835336487165</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>0.520685151282691</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>51.73</t>
+          <t>0.51730304551646</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>51.24</t>
+          <t>0.512367965452671</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>0.498914654158309</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>0.511788009305094</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>0.550174601269312</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54.79</t>
+          <t>0.547905426901681</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>54.64</t>
+          <t>0.546352186369959</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>0.54110409995312</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>53.73</t>
+          <t>0.537348790411007</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>53.54</t>
+          <t>0.535359845367898</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>52.89</t>
+          <t>0.528875058149679</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>52.01</t>
+          <t>0.520061514850739</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>52.23</t>
+          <t>0.522272050510547</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>0.519671129621698</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>0.520469255699721</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>0.520469255699721</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>0.520469255699721</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>0.520469255699721</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>52.05</t>
+          <t>0.520469255699721</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>39.54</t>
+          <t>0.395435887609196</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>38.34</t>
+          <t>0.38342851434867</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>38.03</t>
+          <t>0.380282172559611</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>0.361827995096396</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>35.24</t>
+          <t>0.352434866278116</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>35.84</t>
+          <t>0.358384869020169</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>0.35072937504821</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>32.52</t>
+          <t>0.325179846556404</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>0.320451863736368</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>0.320102225013342</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>0.312774166338327</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>0.312774166338327</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>0.312774166338327</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>0.312774166338327</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>0.312774166338327</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>0.506549288430407</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>51.37</t>
+          <t>0.513667978527083</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>51.82</t>
+          <t>0.518182771576184</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>0.522967324742578</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>0.540044830272503</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>0.53712858467267</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>0.534966344389864</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>0.528275162064775</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>0.508974644900184</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>50.89</t>
+          <t>0.508910915288742</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>0.496966817573052</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>0.494652298290051</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>47.31</t>
+          <t>0.473078588627013</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>0.469788667811106</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>45.65</t>
+          <t>0.456498821086226</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>0.33759136599498</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>0.361820816742457</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>0.405746409850046</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>0.447907356028382</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>0.486189353014669</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>0.481046406956627</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>47.57</t>
+          <t>0.475736647028801</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>47.33</t>
+          <t>0.473304982151526</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>0.520989003731623</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>0.433652498726086</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>0.42243481728854</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>0.447836927373605</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>0.423513959642238</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>0.436306274916245</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>39.99</t>
+          <t>0.399931881746181</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>53.41</t>
+          <t>0.534062504854139</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>54.11</t>
+          <t>0.541146395319888</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>0.544320622973234</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>0.547280166826952</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>56.56</t>
+          <t>0.565590384004276</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>0.563015411685454</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>56.15</t>
+          <t>0.561496213729955</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>55.64</t>
+          <t>0.55640918337804</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>58.27</t>
+          <t>0.582681281560562</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>55.58</t>
+          <t>0.555757369055775</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>0.573952987120466</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>56.53</t>
+          <t>0.565330521220891</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>0.535555794567723</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>49.92</t>
+          <t>0.499240725959773</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>50.87</t>
+          <t>0.508710318894633</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>0.426320073955752</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.428647779424658</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>0.449167982673274</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>0.446070335943492</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>0.446251889212711</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>44.58</t>
+          <t>0.445772631053733</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>0.457460727500405</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>0.461838653075254</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>46.88</t>
+          <t>0.468779209233201</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>47.87</t>
+          <t>0.478726351207042</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>0.482980534274965</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>0.495711131347982</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>0.495711131347982</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>0.495711131347982</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>0.495711131347982</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.223112108065907</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>0.23076560909183</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>0.222322563509499</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213259917236434</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>0.230516427377225</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>0.236222063272243</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>0.243682664860547</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.24066817692975</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>0.235794531713251</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246454552404253</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246466736759821</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>0.255423644330556</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.247899377409721</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>0.244786230180686</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>0.261406427925119</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>0.492977085750473</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>48.34</t>
+          <t>0.483400148700067</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>46.14</t>
+          <t>0.461393561175035</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>46.45</t>
+          <t>0.464486610585819</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>44.18</t>
+          <t>0.441778539288771</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>43.74</t>
+          <t>0.437445925808806</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>44.53</t>
+          <t>0.445283348723593</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>43.99</t>
+          <t>0.439858066104774</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>0.412246956629046</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>39.65</t>
+          <t>0.3964567501294</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>0.394371283380777</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>0.396659953616679</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>40.15</t>
+          <t>0.401534822577419</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>0.382705964454534</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>0.376962701907767</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>0.715398289341023</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>0.715398289341023</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>0.715398289341023</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>0.715398289341023</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>0.715398289341023</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>0.715398289341023</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>0.696262296160517</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>68.54</t>
+          <t>0.685409189560786</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>0.66430498832247</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>0.636013794438747</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>0.62332339219328</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>0.614254002327394</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>60.72</t>
+          <t>0.607154539584167</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>0.600660556376035</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>0.577962927126779</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.223112108065907</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>0.23076560909183</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>0.222322563509499</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213259917236434</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>0.230516427377225</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>0.236222063272243</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>0.243682664860547</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.24066817692975</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>0.235794531713251</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246454552404253</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246466736759821</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>0.255423644330556</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.247899377409721</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>0.244786230180686</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>0.261406427925119</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>0.223112108065907</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>0.23076560909183</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>0.222322563509499</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213259917236434</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>0.230516427377225</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>0.236222063272243</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>0.243682664860547</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.24066817692975</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>0.235794531713251</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246454552404253</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>0.246466736759821</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>0.255423644330556</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.247899377409721</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>0.244786230180686</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>0.261406427925119</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>0.733446005535832</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>0.733446005535832</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>0.733446005535832</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>0.733446005535832</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>0.729936332355163</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>0.727810559025382</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>72.64</t>
+          <t>0.726362175132217</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>0.722046815742873</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>72.03</t>
+          <t>0.720266864953182</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>71.94</t>
+          <t>0.719413033162062</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>0.717240532251261</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>0.717240532251261</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>0.717240532251261</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>0.717240532251261</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>71.72</t>
+          <t>0.717240532251261</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>0.739375755656045</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>0.739375755656045</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>0.739375755656045</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>0.739375755656045</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>75.86</t>
+          <t>0.758607201303084</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>76.04</t>
+          <t>0.760417533827923</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>0.756460306944286</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.09</t>
+          <t>0.760932507933667</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>0.750379657492174</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>74.33</t>
+          <t>0.743270007215774</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>0.722407010337644</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>71.28</t>
+          <t>0.71277079806886</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>0.714076797748988</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>0.712858725275345</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>0.703015142324325</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>0.626242944328873</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>0.626242944328873</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>0.626242944328873</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.62</t>
+          <t>0.626242944328873</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>62.41</t>
+          <t>0.624111470054713</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>60.59</t>
+          <t>0.605906997475185</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>64.88</t>
+          <t>0.64876871144112</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>62.75</t>
+          <t>0.627470352165021</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0.599965997808565</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>0.588610460310025</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>0.582896068714795</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>0.573375334147349</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>0.567629617472114</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>55.41</t>
+          <t>0.554090086471366</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>53.53</t>
+          <t>0.535256145902856</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>59.57</t>
+          <t>0.595686295761917</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>59.72</t>
+          <t>0.597197672815913</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>59.65</t>
+          <t>0.59651254627171</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>0.596031432577136</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>0.582581363577168</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>0.571963368879507</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>56.64</t>
+          <t>0.566430318150786</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>56.05</t>
+          <t>0.560450042836751</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>55.97</t>
+          <t>0.559692976091991</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>55.03</t>
+          <t>0.550289334495076</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>53.68</t>
+          <t>0.53682564494479</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>0.522531436565446</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>0.518849539404371</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>50.38</t>
+          <t>0.503813541998521</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>47.56</t>
+          <t>0.475587232730029</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>0.283281174767894</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>0.29264753677969</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>0.287191318938563</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>0.303036856723649</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>0.296998307345724</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>0.304184435294129</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>0.308225934548862</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>0.309615844246565</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>0.31286926964477</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>0.321687491389864</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>0.321512333986268</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>31.99</t>
+          <t>0.31986816593863</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>32.56</t>
+          <t>0.325593501739573</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>32.83</t>
+          <t>0.328263702439916</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>33.08</t>
+          <t>0.330843112806146</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>0.318819629851009</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>0.31916196227376</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>0.319710133231255</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>0.320454701166242</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>0.321389274686131</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>0.322510114575151</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>0.323815868024402</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>0.325307407095882</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>0.323377791334911</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>0.32160668487598</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>0.315196395604442</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>0.306436702598357</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>0.310202137884426</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>30.31</t>
+          <t>0.303097711892232</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>0.294405386502443</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>0.536539450425186</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>0.539328388650854</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>0.533761083967983</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>53.08</t>
+          <t>0.530822349168993</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>0.527792000424003</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>0.527012066199086</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>0.519733139183468</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>0.514008099533897</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>0.518776588626101</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>0.509619680832761</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.507878752420596</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>0.503183389493176</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>0.505864707394152</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>0.501108006188618</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>49.36</t>
+          <t>0.493573498532951</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>0.481081364027288</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>48.29</t>
+          <t>0.482914782999773</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>0.484508597686212</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>0.484374909721412</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>0.485974399802187</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>0.48451179610014</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>0.4827588095723</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>0.478284710942443</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>47.52</t>
+          <t>0.475169752304089</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>0.468603305195726</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>0.464942577376845</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>0.461986680306437</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>0.457044841299505</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>45.15</t>
+          <t>0.451477972645133</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>44.48</t>
+          <t>0.444806278159611</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>0.463667964044721</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>0.466754028426433</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>0.468371309821971</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>46.83</t>
+          <t>0.468343276562881</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>0.471208454264456</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>0.471064679839769</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>0.47013320487999</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>46.65</t>
+          <t>0.466470782425614</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>0.464642704475651</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.459175681330757</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>0.456677283528056</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>45.47</t>
+          <t>0.454664515077834</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>0.450251726895401</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>0.445197470725994</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>0.440419253199192</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
